--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G557"/>
+  <dimension ref="A1:G562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15475,6 +15475,141 @@
         <v>398.37</v>
       </c>
       <c r="G557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="C558" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="D558" t="n">
+        <v>393.22</v>
+      </c>
+      <c r="E558" t="n">
+        <v>396.97</v>
+      </c>
+      <c r="F558" t="n">
+        <v>398.27</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>379.57</v>
+      </c>
+      <c r="C559" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="D559" t="n">
+        <v>393.62</v>
+      </c>
+      <c r="E559" t="n">
+        <v>397.62</v>
+      </c>
+      <c r="F559" t="n">
+        <v>398.11</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="C560" t="n">
+        <v>383.28</v>
+      </c>
+      <c r="D560" t="n">
+        <v>393.77</v>
+      </c>
+      <c r="E560" t="n">
+        <v>398.44</v>
+      </c>
+      <c r="F560" t="n">
+        <v>398.66</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>380.42</v>
+      </c>
+      <c r="C561" t="n">
+        <v>383.55</v>
+      </c>
+      <c r="D561" t="n">
+        <v>394.39</v>
+      </c>
+      <c r="E561" t="n">
+        <v>398.79</v>
+      </c>
+      <c r="F561" t="n">
+        <v>398.85</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>380.48</v>
+      </c>
+      <c r="C562" t="n">
+        <v>384</v>
+      </c>
+      <c r="D562" t="n">
+        <v>394.72</v>
+      </c>
+      <c r="E562" t="n">
+        <v>399.02</v>
+      </c>
+      <c r="F562" t="n">
+        <v>398.33</v>
+      </c>
+      <c r="G562" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15491,7 +15626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B634"/>
+  <dimension ref="A1:B639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21834,6 +21969,56 @@
       </c>
       <c r="B634" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -22002,28 +22187,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1285894655068082</v>
+        <v>0.1243598476474353</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06755790657053695</v>
+        <v>0.06423502162343586</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86857645928073</v>
+        <v>2.864991986701725</v>
       </c>
       <c r="N2" t="n">
-        <v>13.86190963442748</v>
+        <v>13.80471074920441</v>
       </c>
       <c r="O2" t="n">
-        <v>3.723158556176124</v>
+        <v>3.715469115630543</v>
       </c>
       <c r="P2" t="n">
-        <v>378.9696094479206</v>
+        <v>379.0134851483527</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22080,28 +22265,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1871304657808862</v>
+        <v>0.1817297192613378</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1519412248066331</v>
+        <v>0.1456860928603798</v>
       </c>
       <c r="M3" t="n">
-        <v>2.810775115817306</v>
+        <v>2.818990711420217</v>
       </c>
       <c r="N3" t="n">
-        <v>11.87150884489777</v>
+        <v>11.86651868136836</v>
       </c>
       <c r="O3" t="n">
-        <v>3.445505600764243</v>
+        <v>3.444781369168203</v>
       </c>
       <c r="P3" t="n">
-        <v>381.838340915247</v>
+        <v>381.8943725045964</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22158,28 +22343,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01427610179507694</v>
+        <v>0.01435822152138857</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001429077525791578</v>
+        <v>0.001470894276739743</v>
       </c>
       <c r="M4" t="n">
-        <v>2.299731232634274</v>
+        <v>2.283459255380267</v>
       </c>
       <c r="N4" t="n">
-        <v>8.649858282425472</v>
+        <v>8.575364817531328</v>
       </c>
       <c r="O4" t="n">
-        <v>2.941064141161405</v>
+        <v>2.928372383685403</v>
       </c>
       <c r="P4" t="n">
-        <v>393.5108507329039</v>
+        <v>393.5099921837389</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22236,28 +22421,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05434122901438122</v>
+        <v>-0.05323226739684085</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02134029440320839</v>
+        <v>0.02083095866436946</v>
       </c>
       <c r="M5" t="n">
-        <v>2.325443213280896</v>
+        <v>2.312807898306875</v>
       </c>
       <c r="N5" t="n">
-        <v>8.225395851263745</v>
+        <v>8.161507475068401</v>
       </c>
       <c r="O5" t="n">
-        <v>2.867995092615004</v>
+        <v>2.856835220146308</v>
       </c>
       <c r="P5" t="n">
-        <v>398.9348640970946</v>
+        <v>398.9233488752905</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22314,28 +22499,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2899414979298609</v>
+        <v>-0.2928739141570225</v>
       </c>
       <c r="J6" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="K6" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0861277692920448</v>
+        <v>0.0891076956446718</v>
       </c>
       <c r="M6" t="n">
-        <v>5.784407516257978</v>
+        <v>5.745406010075918</v>
       </c>
       <c r="N6" t="n">
-        <v>54.17883125241834</v>
+        <v>53.72609045411982</v>
       </c>
       <c r="O6" t="n">
-        <v>7.360627096410899</v>
+        <v>7.329808350435898</v>
       </c>
       <c r="P6" t="n">
-        <v>408.0929653061941</v>
+        <v>408.1233887715101</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22373,7 +22558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G557"/>
+  <dimension ref="A1:G562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42985,6 +43170,191 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-35.01262926851037,173.85260590863993</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-35.01303393880515,173.85331896672568</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-35.013260363759386,173.85414948662688</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-35.013499783674945,173.85488628466769</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-35.01341949421791,173.855674193142</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-35.01262114471462,173.85261356355488</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-35.01303125165265,173.85332097820725</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-35.0132570819537,173.85415130498572</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-35.01349399439842,173.85488739485075</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-35.013420929966124,173.85567436482177</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-35.012618436782596,173.85261611519286</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-35.013032633616795,173.85331994373104</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-35.01325585127657,173.85415198687028</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-35.013486691003386,173.85488879538917</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-35.013415994581685,173.8556737746726</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-35.01261508749818,173.85261927116593</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-35.01303056067058,173.85332149544533</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-35.01325076447767,173.85415480532612</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-35.01348357370061,173.8548893931799</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-35.013414289630695,173.8556735708029</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-35.01261465992996,173.8526196740561</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-35.01302710576016,173.85332408163566</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-35.013248056987926,173.85415630547183</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-35.01348152518738,173.85488978601376</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-35.01341895581234,173.8556741287621</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G562"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15612,6 +15612,87 @@
       <c r="G562" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>381.04</v>
+      </c>
+      <c r="C563" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="D563" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="E563" t="n">
+        <v>399.63</v>
+      </c>
+      <c r="F563" t="n">
+        <v>399.15</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="C564" t="n">
+        <v>384.8</v>
+      </c>
+      <c r="D564" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="E564" t="n">
+        <v>399.83</v>
+      </c>
+      <c r="F564" t="n">
+        <v>399.35</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="C565" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="D565" t="n">
+        <v>396.2</v>
+      </c>
+      <c r="E565" t="n">
+        <v>400.45</v>
+      </c>
+      <c r="F565" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B639"/>
+  <dimension ref="A1:B642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22019,6 +22100,36 @@
       </c>
       <c r="B639" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -22187,28 +22298,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1243598476474353</v>
+        <v>0.1236449812506556</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06423502162343586</v>
+        <v>0.06415030063750182</v>
       </c>
       <c r="M2" t="n">
-        <v>2.864991986701725</v>
+        <v>2.853432980531401</v>
       </c>
       <c r="N2" t="n">
-        <v>13.80471074920441</v>
+        <v>13.73582465463725</v>
       </c>
       <c r="O2" t="n">
-        <v>3.715469115630543</v>
+        <v>3.706187347482214</v>
       </c>
       <c r="P2" t="n">
-        <v>379.0134851483527</v>
+        <v>379.020919905437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22265,28 +22376,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1817297192613378</v>
+        <v>0.1798755002550383</v>
       </c>
       <c r="J3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1456860928603798</v>
+        <v>0.1442035142416302</v>
       </c>
       <c r="M3" t="n">
-        <v>2.818990711420217</v>
+        <v>2.815348900006537</v>
       </c>
       <c r="N3" t="n">
-        <v>11.86651868136836</v>
+        <v>11.82586799627977</v>
       </c>
       <c r="O3" t="n">
-        <v>3.444781369168203</v>
+        <v>3.438875978612746</v>
       </c>
       <c r="P3" t="n">
-        <v>381.8943725045964</v>
+        <v>381.913664043755</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22343,28 +22454,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01435822152138857</v>
+        <v>0.01578268249542981</v>
       </c>
       <c r="J4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001470894276739743</v>
+        <v>0.001792423438766177</v>
       </c>
       <c r="M4" t="n">
-        <v>2.283459255380267</v>
+        <v>2.278841689223316</v>
       </c>
       <c r="N4" t="n">
-        <v>8.575364817531328</v>
+        <v>8.543507992468479</v>
       </c>
       <c r="O4" t="n">
-        <v>2.928372383685403</v>
+        <v>2.922927982771467</v>
       </c>
       <c r="P4" t="n">
-        <v>393.5099921837389</v>
+        <v>393.4951618783771</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22421,28 +22532,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05323226739684085</v>
+        <v>-0.05088606894693344</v>
       </c>
       <c r="J5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K5" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02083095866436946</v>
+        <v>0.01918962898117893</v>
       </c>
       <c r="M5" t="n">
-        <v>2.312807898306875</v>
+        <v>2.313769348300693</v>
       </c>
       <c r="N5" t="n">
-        <v>8.161507475068401</v>
+        <v>8.150994843230771</v>
       </c>
       <c r="O5" t="n">
-        <v>2.856835220146308</v>
+        <v>2.854994718599453</v>
       </c>
       <c r="P5" t="n">
-        <v>398.9233488752905</v>
+        <v>398.8989280255995</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22499,28 +22610,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2928739141570225</v>
+        <v>-0.293668682467506</v>
       </c>
       <c r="J6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K6" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0891076956446718</v>
+        <v>0.09039823093949351</v>
       </c>
       <c r="M6" t="n">
-        <v>5.745406010075918</v>
+        <v>5.71820907254085</v>
       </c>
       <c r="N6" t="n">
-        <v>53.72609045411982</v>
+        <v>53.4442488199124</v>
       </c>
       <c r="O6" t="n">
-        <v>7.329808350435898</v>
+        <v>7.310557353575198</v>
       </c>
       <c r="P6" t="n">
-        <v>408.1233887715101</v>
+        <v>408.1316582341714</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22558,7 +22669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G562"/>
+  <dimension ref="A1:G565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43355,6 +43466,117 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-35.01261066929309,173.85262343436403</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-35.013026721881204,173.85332436899014</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-35.013247646762196,173.85415653276664</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-35.01347609217397,173.85489082787743</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-35.01341159760281,173.8556732489034</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-35.012607676315355,173.85262625459478</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-35.01302096369705,173.85332867930686</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-35.01324370859525,173.85415871479657</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-35.013474310858086,173.85489116947204</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-35.013409802917565,173.85567303430375</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-35.01260147657559,173.85263209650063</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-35.013014360979014,173.8533336218026</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-35.01323591430636,173.8541630333969</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-35.01346878877888,173.85489222841528</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-35.013407200623945,173.85567272313426</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G565"/>
+  <dimension ref="A1:G568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15693,6 +15693,87 @@
       <c r="G565" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="C566" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D566" t="n">
+        <v>396.5</v>
+      </c>
+      <c r="E566" t="n">
+        <v>401.06</v>
+      </c>
+      <c r="F566" t="n">
+        <v>398.89</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>382.43</v>
+      </c>
+      <c r="C567" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="D567" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="E567" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="F567" t="n">
+        <v>398.89</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="C568" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="D568" t="n">
+        <v>396.38</v>
+      </c>
+      <c r="E568" t="n">
+        <v>401.52</v>
+      </c>
+      <c r="F568" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B642"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22130,6 +22211,36 @@
       </c>
       <c r="B642" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -22298,28 +22409,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1236449812506556</v>
+        <v>0.1238923607710684</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K2" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06415030063750182</v>
+        <v>0.06501801857423672</v>
       </c>
       <c r="M2" t="n">
-        <v>2.853432980531401</v>
+        <v>2.839825872976782</v>
       </c>
       <c r="N2" t="n">
-        <v>13.73582465463725</v>
+        <v>13.66376333035682</v>
       </c>
       <c r="O2" t="n">
-        <v>3.706187347482214</v>
+        <v>3.696452803750755</v>
       </c>
       <c r="P2" t="n">
-        <v>379.020919905437</v>
+        <v>379.018330236009</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22376,28 +22487,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1798755002550383</v>
+        <v>0.1790471463090683</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K3" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1442035142416302</v>
+        <v>0.1443026269854353</v>
       </c>
       <c r="M3" t="n">
-        <v>2.815348900006537</v>
+        <v>2.80545708863404</v>
       </c>
       <c r="N3" t="n">
-        <v>11.82586799627977</v>
+        <v>11.76772555232191</v>
       </c>
       <c r="O3" t="n">
-        <v>3.438875978612746</v>
+        <v>3.430411863365958</v>
       </c>
       <c r="P3" t="n">
-        <v>381.913664043755</v>
+        <v>381.922321470931</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22454,28 +22565,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01578268249542981</v>
+        <v>0.0181884464250079</v>
       </c>
       <c r="J4" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001792423438766177</v>
+        <v>0.00239431489992048</v>
       </c>
       <c r="M4" t="n">
-        <v>2.278841689223316</v>
+        <v>2.279538357946098</v>
       </c>
       <c r="N4" t="n">
-        <v>8.543507992468479</v>
+        <v>8.532584942052699</v>
       </c>
       <c r="O4" t="n">
-        <v>2.922927982771467</v>
+        <v>2.921058873431465</v>
       </c>
       <c r="P4" t="n">
-        <v>393.4951618783771</v>
+        <v>393.4700091346469</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22532,28 +22643,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05088606894693344</v>
+        <v>-0.04737593345001554</v>
       </c>
       <c r="J5" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01918962898117893</v>
+        <v>0.01669979319063697</v>
       </c>
       <c r="M5" t="n">
-        <v>2.313769348300693</v>
+        <v>2.321274823239043</v>
       </c>
       <c r="N5" t="n">
-        <v>8.150994843230771</v>
+        <v>8.180924042133224</v>
       </c>
       <c r="O5" t="n">
-        <v>2.854994718599453</v>
+        <v>2.860231466530851</v>
       </c>
       <c r="P5" t="n">
-        <v>398.8989280255995</v>
+        <v>398.8622245092099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22610,28 +22721,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.293668682467506</v>
+        <v>-0.2945363950130308</v>
       </c>
       <c r="J6" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K6" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09039823093949351</v>
+        <v>0.0917391881876316</v>
       </c>
       <c r="M6" t="n">
-        <v>5.71820907254085</v>
+        <v>5.691578842740129</v>
       </c>
       <c r="N6" t="n">
-        <v>53.4442488199124</v>
+        <v>53.16739479327679</v>
       </c>
       <c r="O6" t="n">
-        <v>7.310557353575198</v>
+        <v>7.291597547401858</v>
       </c>
       <c r="P6" t="n">
-        <v>408.1316582341714</v>
+        <v>408.1407230894749</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22669,7 +22780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G565"/>
+  <dimension ref="A1:G568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43577,6 +43688,117 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-35.0126001226094,173.85263337231905</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-35.013014821633774,173.85333327697734</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-35.013233452951944,173.85416439716525</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-35.01346335576545,173.85489327027864</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-35.013413930693645,173.855673527883</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-35.012600763961814,173.852632767984</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-35.01301282546317,173.8533347712201</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-35.013232714545616,173.85416480629573</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-35.01346210884434,173.8548935093948</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-35.013413930693645,173.855673527883</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-35.012597129631445,173.85263619254903</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-35.01300983120724,173.8533370125841</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-35.013234437493715,173.85416385165792</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-35.013459258738926,173.854894055946</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-35.01340414965902,173.85567235831488</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
